--- a/TPG Inc - Corporate Tree - Obligors (filtered).xlsx
+++ b/TPG Inc - Corporate Tree - Obligors (filtered).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,28 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,6 +628,14 @@
   </sheetPr>
   <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1"/>
     <row r="2"/>
@@ -622,37 +648,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Has an Obligor</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Has or Is Obligor</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Is its own Obligor</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Has another Obligor</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Is Obligor for another entity</t>
         </is>
@@ -672,9 +698,9 @@
           <t>69886004</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -687,7 +713,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -699,7 +725,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TPG Capital LP/US</t>
+          <t xml:space="preserve">  TPG Capital LP/US</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,22 +733,22 @@
           <t>233605</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -734,7 +760,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BVI Holdings Ltd</t>
+          <t xml:space="preserve">    BVI Holdings Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -742,22 +768,22 @@
           <t>63179654</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -769,7 +795,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BVI Holdings Mayfair Ltd</t>
+          <t xml:space="preserve">      BVI Holdings Mayfair Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -777,9 +803,9 @@
           <t>63179438</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -792,7 +818,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -804,7 +830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BVI Holdings Kensington Ltd</t>
+          <t xml:space="preserve">        BVI Holdings Kensington Ltd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -812,22 +838,22 @@
           <t>63198241</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -839,7 +865,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BVI Audley Inc</t>
+          <t xml:space="preserve">          BVI Audley Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -847,22 +873,22 @@
           <t>63198283</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -874,7 +900,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BVI Oxford Inc</t>
+          <t xml:space="preserve">            BVI Oxford Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -882,22 +908,22 @@
           <t>63198289</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -909,7 +935,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Convey Health Solutions Holdings LLC</t>
+          <t xml:space="preserve">    Convey Health Solutions Holdings LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -917,22 +943,22 @@
           <t>8727696</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -944,7 +970,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Envision Pharmaceutical Holdings Inc</t>
+          <t xml:space="preserve">    Envision Pharmaceutical Holdings Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -952,22 +978,22 @@
           <t>36223919</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -979,7 +1005,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Envision Acquisition Co LLC</t>
+          <t xml:space="preserve">      Envision Acquisition Co LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -987,22 +1013,22 @@
           <t>36775326</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1014,7 +1040,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VF Holdings Corp</t>
+          <t xml:space="preserve">    VF Holdings Corp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1022,22 +1048,22 @@
           <t>20861838</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1049,7 +1075,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Taco Bueno Restaurants LP</t>
+          <t xml:space="preserve">    Taco Bueno Restaurants LP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1057,22 +1083,22 @@
           <t>1709629</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1084,7 +1110,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frank Recruitment Group Ltd</t>
+          <t xml:space="preserve">    Frank Recruitment Group Ltd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1092,22 +1118,22 @@
           <t>39588649</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1119,7 +1145,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gate Gourmet International AG</t>
+          <t xml:space="preserve">    Gate Gourmet International AG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1127,22 +1153,22 @@
           <t>7700980</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1154,7 +1180,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ensemble Holdings Inc</t>
+          <t xml:space="preserve">    Ensemble Holdings Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1162,7 +1188,7 @@
           <t>50651121</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1177,7 +1203,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1189,7 +1215,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sophia Holding I LP</t>
+          <t xml:space="preserve">      Sophia Holding I LP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1197,7 +1223,7 @@
           <t>29553009</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1212,7 +1238,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1224,7 +1250,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sophia Holding Finance LP</t>
+          <t xml:space="preserve">        Sophia Holding Finance LP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,22 +1258,22 @@
           <t>38099473</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1259,7 +1285,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sophia Holding II LP</t>
+          <t xml:space="preserve">          Sophia Holding II LP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1267,22 +1293,22 @@
           <t>29553001</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1294,7 +1320,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sophia Holding Finance LP / Sophia Holding Finance Inc</t>
+          <t xml:space="preserve">          Sophia Holding Finance LP / Sophia Holding Finance Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1302,22 +1328,22 @@
           <t>38018592</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1329,7 +1355,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sophia Holding Finance Inc</t>
+          <t xml:space="preserve">          Sophia Holding Finance Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1337,22 +1363,22 @@
           <t>38099485</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1364,7 +1390,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dolcetto TopCo Sarl</t>
+          <t xml:space="preserve">    Dolcetto TopCo Sarl</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1372,7 +1398,7 @@
           <t>73191975</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1387,7 +1413,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1399,7 +1425,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dolcetto MidCo Sarl</t>
+          <t xml:space="preserve">      Dolcetto MidCo Sarl</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1407,7 +1433,7 @@
           <t>73191972</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1422,7 +1448,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1434,7 +1460,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dolcetto HoldCo 1 Sarl</t>
+          <t xml:space="preserve">        Dolcetto HoldCo 1 Sarl</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1442,7 +1468,7 @@
           <t>73191968</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1457,7 +1483,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1469,7 +1495,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dolcetto HoldCo 2 Sarl</t>
+          <t xml:space="preserve">          Dolcetto HoldCo 2 Sarl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1477,7 +1503,7 @@
           <t>73191964</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1492,7 +1518,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1504,7 +1530,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dolcetto Holdco SpA</t>
+          <t xml:space="preserve">            Dolcetto Holdco SpA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1512,22 +1538,22 @@
           <t>70541652</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1539,7 +1565,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TPG Europe LLP</t>
+          <t xml:space="preserve">    TPG Europe LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1547,7 +1573,7 @@
           <t>13000230</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1562,7 +1588,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1574,7 +1600,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TES Global Investments Sarl</t>
+          <t xml:space="preserve">      TES Global Investments Sarl</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1582,7 +1608,7 @@
           <t>50772166</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1597,7 +1623,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1609,7 +1635,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TES Global Financial Sarl</t>
+          <t xml:space="preserve">        TES Global Financial Sarl</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1617,22 +1643,22 @@
           <t>36807194</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1644,7 +1670,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Axip Energy Services LP</t>
+          <t xml:space="preserve">    Axip Energy Services LP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1652,22 +1678,22 @@
           <t>13946714</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1679,7 +1705,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vita Cayman Ltd</t>
+          <t xml:space="preserve">    Vita Cayman Ltd</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1687,7 +1713,7 @@
           <t>24106637</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1702,7 +1728,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1714,7 +1740,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vita Lux III Sarl</t>
+          <t xml:space="preserve">      Vita Lux III Sarl</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1722,22 +1748,22 @@
           <t>20857482</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1749,7 +1775,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vita Holdings Ltd</t>
+          <t xml:space="preserve">        Vita Holdings Ltd</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1757,7 +1783,7 @@
           <t>12973366</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1772,7 +1798,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1784,7 +1810,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vita Group UnLtd</t>
+          <t xml:space="preserve">          Vita Group UnLtd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1792,22 +1818,22 @@
           <t>111282</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1819,7 +1845,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vita International Ltd</t>
+          <t xml:space="preserve">            Vita International Ltd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1827,7 +1853,7 @@
           <t>12488026</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1842,7 +1868,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1854,7 +1880,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vita Germany GmbH</t>
+          <t xml:space="preserve">              Vita Germany GmbH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1862,22 +1888,22 @@
           <t>20868127</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1889,7 +1915,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>British Vita Netherlands BV</t>
+          <t xml:space="preserve">        British Vita Netherlands BV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1897,22 +1923,22 @@
           <t>20868167</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1924,7 +1950,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Axcan Holdings Inc</t>
+          <t xml:space="preserve">    Axcan Holdings Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1932,22 +1958,22 @@
           <t>14545571</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1959,7 +1985,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Axcan MidCo Inc</t>
+          <t xml:space="preserve">      Axcan MidCo Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1967,22 +1993,22 @@
           <t>14545575</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1994,7 +2020,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IVD Holdings Inc</t>
+          <t xml:space="preserve">    IVD Holdings Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2002,7 +2028,7 @@
           <t>30269287</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2017,7 +2043,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2029,7 +2055,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IVD Intermediate Holdings A Inc</t>
+          <t xml:space="preserve">      IVD Intermediate Holdings A Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2037,7 +2063,7 @@
           <t>30493841</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2052,7 +2078,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2064,7 +2090,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IVD Intermediate Holdings B Inc</t>
+          <t xml:space="preserve">        IVD Intermediate Holdings B Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2072,22 +2098,22 @@
           <t>30269297</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2099,7 +2125,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>InvoCare Pty Ltd</t>
+          <t xml:space="preserve">    InvoCare Pty Ltd</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2107,22 +2133,22 @@
           <t>8432302</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2134,7 +2160,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>InvoCare Australia Pty Ltd</t>
+          <t xml:space="preserve">      InvoCare Australia Pty Ltd</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2142,22 +2168,22 @@
           <t>16734833</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2169,7 +2195,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intervest SA</t>
+          <t xml:space="preserve">    Intervest SA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2177,22 +2203,22 @@
           <t>812513</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2204,7 +2230,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RCN Telecom Services LLC</t>
+          <t xml:space="preserve">    RCN Telecom Services LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2212,22 +2238,22 @@
           <t>33221180</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2239,7 +2265,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RCN Capital Corp</t>
+          <t xml:space="preserve">      RCN Capital Corp</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2247,22 +2273,22 @@
           <t>52149513</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2274,7 +2300,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RCN Telecom Services LLC / RCN Capital Corp</t>
+          <t xml:space="preserve">      RCN Telecom Services LLC / RCN Capital Corp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2282,22 +2308,22 @@
           <t>36419056</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2309,7 +2335,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WaveDivision Holdings LLC</t>
+          <t xml:space="preserve">      WaveDivision Holdings LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2317,22 +2343,22 @@
           <t>8139330</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2344,7 +2370,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WaveDivision Escrow Corp</t>
+          <t xml:space="preserve">        WaveDivision Escrow Corp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2352,22 +2378,22 @@
           <t>53937391</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2379,7 +2405,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WaveDivision Escrow LLC / WaveDivision Escrow Corp</t>
+          <t xml:space="preserve">        WaveDivision Escrow LLC / WaveDivision Escrow Corp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2387,22 +2413,22 @@
           <t>32227872</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2414,7 +2440,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WaveDivision Escrow LLC</t>
+          <t xml:space="preserve">        WaveDivision Escrow LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2422,22 +2448,22 @@
           <t>53937367</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2449,7 +2475,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jonah Energy LLC</t>
+          <t xml:space="preserve">    Jonah Energy LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2457,22 +2483,22 @@
           <t>40129417</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2484,7 +2510,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tap Rock Resources LLC</t>
+          <t xml:space="preserve">      Tap Rock Resources LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2492,22 +2518,22 @@
           <t>56221776</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2519,7 +2545,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jonah Energy Finance Corp</t>
+          <t xml:space="preserve">      Jonah Energy Finance Corp</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2527,22 +2553,22 @@
           <t>55095647</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2554,7 +2580,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jonah Energy LLC / Jonah Energy Finance Corp</t>
+          <t xml:space="preserve">      Jonah Energy LLC / Jonah Energy Finance Corp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2562,22 +2588,22 @@
           <t>55087541</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2589,7 +2615,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TPG Growth LLC</t>
+          <t xml:space="preserve">    TPG Growth LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2597,7 +2623,7 @@
           <t>18307190</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2612,7 +2638,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2624,7 +2650,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mendocino Farms LLC</t>
+          <t xml:space="preserve">      Mendocino Farms LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2632,22 +2658,22 @@
           <t>29079179</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2659,7 +2685,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SmartSweets Inc</t>
+          <t xml:space="preserve">      SmartSweets Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2667,22 +2693,22 @@
           <t>69184377</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2694,7 +2720,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CLEAResult Consulting Inc</t>
+          <t xml:space="preserve">      CLEAResult Consulting Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2702,22 +2728,22 @@
           <t>20827887</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2729,7 +2755,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TPG Growth II LP</t>
+          <t xml:space="preserve">      TPG Growth II LP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2737,22 +2763,22 @@
           <t>29277506</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2764,7 +2790,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Delinea Inc</t>
+          <t xml:space="preserve">      Delinea Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2772,22 +2798,22 @@
           <t>24747149</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2799,7 +2825,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Denali Water Solutions LLC</t>
+          <t xml:space="preserve">      Denali Water Solutions LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2807,22 +2833,22 @@
           <t>45992980</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2834,7 +2860,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Morrow Sodali Global LLC</t>
+          <t xml:space="preserve">      Morrow Sodali Global LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2842,22 +2868,22 @@
           <t>50823010</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2869,7 +2895,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sodali Inc</t>
+          <t xml:space="preserve">        Sodali Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2877,7 +2903,7 @@
           <t>49809726</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2892,7 +2918,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2904,7 +2930,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Morrow &amp; Co Inc</t>
+          <t xml:space="preserve">          Morrow &amp; Co Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2912,22 +2938,22 @@
           <t>805789</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2939,7 +2965,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sodali &amp; Co Ltd</t>
+          <t xml:space="preserve">        Sodali &amp; Co Ltd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2947,22 +2973,22 @@
           <t>48589037</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2974,7 +3000,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ATE XIII Norte Brasil Transmissora de Energia SA</t>
+          <t xml:space="preserve">    ATE XIII Norte Brasil Transmissora de Energia SA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2982,22 +3008,22 @@
           <t>20971681</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3009,7 +3035,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Directv Entertainment Holdings LLC</t>
+          <t xml:space="preserve">    Directv Entertainment Holdings LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3017,7 +3043,7 @@
           <t>69792299</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3032,7 +3058,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3044,7 +3070,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Directv Financing Co-Obligor Inc</t>
+          <t xml:space="preserve">      Directv Financing Co-Obligor Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3052,22 +3078,22 @@
           <t>69670417</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3079,7 +3105,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Directv Financing LLC</t>
+          <t xml:space="preserve">      Directv Financing LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3087,22 +3113,22 @@
           <t>69642135</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3114,7 +3140,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Directv Financing LLC / Directv Financing Co-Obligor Inc</t>
+          <t xml:space="preserve">        Directv Financing LLC / Directv Financing Co-Obligor Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3122,22 +3148,22 @@
           <t>69865297</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3149,7 +3175,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TPG VII CDS Holdings LP</t>
+          <t xml:space="preserve">    TPG VII CDS Holdings LP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3157,7 +3183,7 @@
           <t>51055973</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3172,7 +3198,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3184,7 +3210,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cirque du Soleil Holdings LP</t>
+          <t xml:space="preserve">      Cirque du Soleil Holdings LP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3192,7 +3218,7 @@
           <t>51056549</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3207,7 +3233,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3219,7 +3245,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cirque du Soleil Inc</t>
+          <t xml:space="preserve">        Cirque du Soleil Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3227,22 +3253,22 @@
           <t>911626</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3254,7 +3280,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CDS US Holdings Inc</t>
+          <t xml:space="preserve">        CDS US Holdings Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3262,7 +3288,7 @@
           <t>51043113</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3277,7 +3303,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3289,7 +3315,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Formercs US Intermediate Holdings Inc</t>
+          <t xml:space="preserve">          Formercs US Intermediate Holdings Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3297,22 +3323,22 @@
           <t>45877694</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3324,7 +3350,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Celerity Group Inc</t>
+          <t xml:space="preserve">    Celerity Group Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3332,22 +3358,22 @@
           <t>7756384</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3359,7 +3385,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Project Ruby Ultimate Parent Corp</t>
+          <t xml:space="preserve">    Project Ruby Ultimate Parent Corp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3367,22 +3393,22 @@
           <t>52459187</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3394,7 +3420,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wellsky Corp</t>
+          <t xml:space="preserve">      Wellsky Corp</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3402,22 +3428,22 @@
           <t>105304</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3429,7 +3455,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Assisted Living Concepts LLC</t>
+          <t xml:space="preserve">    Assisted Living Concepts LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3437,22 +3463,22 @@
           <t>10838597</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3464,7 +3490,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ALC Three LLC</t>
+          <t xml:space="preserve">      ALC Three LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3472,22 +3498,22 @@
           <t>16495211</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3499,7 +3525,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Beaver-Visitec International Inc</t>
+          <t xml:space="preserve">    Beaver-Visitec International Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3507,22 +3533,22 @@
           <t>20536686</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3534,7 +3560,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BVI Medical Inc</t>
+          <t xml:space="preserve">      BVI Medical Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3542,22 +3568,22 @@
           <t>24726180</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3569,7 +3595,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>En-Touch Systems Inc</t>
+          <t xml:space="preserve">    En-Touch Systems Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3577,22 +3603,22 @@
           <t>11088377</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3604,7 +3630,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IASIS Investment LLC</t>
+          <t xml:space="preserve">    IASIS Investment LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3612,22 +3638,22 @@
           <t>15170664</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3639,7 +3665,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Field Container Co LP</t>
+          <t xml:space="preserve">    Field Container Co LP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3647,22 +3673,22 @@
           <t>7116029</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3674,7 +3700,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Grande Communications Networks LLC</t>
+          <t xml:space="preserve">    Grande Communications Networks LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3682,22 +3708,22 @@
           <t>14340229</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3709,7 +3735,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Newbridge Capital LLC</t>
+          <t xml:space="preserve">    Newbridge Capital LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3717,22 +3743,22 @@
           <t>874555</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3744,7 +3770,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TPG Real Estate Advisors LLC</t>
+          <t xml:space="preserve">  TPG Real Estate Advisors LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3752,7 +3778,7 @@
           <t>46191401</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3767,7 +3793,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3779,7 +3805,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A&amp;O Hotels and Hostels Holding AG</t>
+          <t xml:space="preserve">    A&amp;O Hotels and Hostels Holding AG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3787,22 +3813,22 @@
           <t>52190372</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3814,7 +3840,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Angelo Gordon Energy Servicer LLC</t>
+          <t xml:space="preserve">  Angelo Gordon Energy Servicer LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3822,22 +3848,22 @@
           <t>66974010</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3849,7 +3875,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SynXis Corp</t>
+          <t xml:space="preserve">  SynXis Corp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3857,22 +3883,22 @@
           <t>953844</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3884,7 +3910,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DIRECTV Holdings LLC</t>
+          <t xml:space="preserve">  DIRECTV Holdings LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3892,22 +3918,22 @@
           <t>8028855</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3919,7 +3945,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DIRECTV Holdings LLC / DIRECTV Financing Co Inc</t>
+          <t xml:space="preserve">    DIRECTV Holdings LLC / DIRECTV Financing Co Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3927,22 +3953,22 @@
           <t>9241739</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3954,7 +3980,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TPG Partners VI LP</t>
+          <t xml:space="preserve">  TPG Partners VI LP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3962,22 +3988,22 @@
           <t>25137214</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3989,7 +4015,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Novotech Health Holdings Pte Ltd</t>
+          <t xml:space="preserve">  Novotech Health Holdings Pte Ltd</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3997,7 +4023,7 @@
           <t>69942434</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4012,7 +4038,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4024,7 +4050,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Novotech SG Holdings Pte Ltd</t>
+          <t xml:space="preserve">    Novotech SG Holdings Pte Ltd</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4032,22 +4058,22 @@
           <t>72747785</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4059,7 +4085,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Matrix Renewables</t>
+          <t xml:space="preserve">  Matrix Renewables</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4067,22 +4093,22 @@
           <t>69497690</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4094,7 +4120,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Energia Solado SL</t>
+          <t xml:space="preserve">    Energia Solado SL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4102,22 +4128,22 @@
           <t>72050164</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4129,7 +4155,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Exactech Inc</t>
+          <t xml:space="preserve">  Exactech Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4137,22 +4163,22 @@
           <t>171753</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4164,7 +4190,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Osteon Merger Sub Inc</t>
+          <t xml:space="preserve">    Osteon Merger Sub Inc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4172,22 +4198,22 @@
           <t>58867132</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4199,7 +4225,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TPG Real Estate Partners III LP</t>
+          <t xml:space="preserve">  TPG Real Estate Partners III LP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4207,22 +4233,22 @@
           <t>55890913</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4234,7 +4260,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DOC Generici Srl</t>
+          <t xml:space="preserve">  DOC Generici Srl</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4242,22 +4268,22 @@
           <t>21204433</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4269,7 +4295,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tarrant Capital IP LLC</t>
+          <t xml:space="preserve">  Tarrant Capital IP LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4277,7 +4303,7 @@
           <t>27198476</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4292,7 +4318,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4304,7 +4330,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Transplace Holdings Inc</t>
+          <t xml:space="preserve">    Transplace Holdings Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4312,22 +4338,22 @@
           <t>55312251</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4339,7 +4365,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nintex Global Ltd/US</t>
+          <t xml:space="preserve">    Nintex Global Ltd/US</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4347,22 +4373,22 @@
           <t>63726124</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4374,7 +4400,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Confluent Medical Technologies Inc</t>
+          <t xml:space="preserve">    Confluent Medical Technologies Inc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4382,22 +4408,22 @@
           <t>15697180</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4409,7 +4435,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TPG Partners IX LP</t>
+          <t xml:space="preserve">  TPG Partners IX LP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4417,22 +4443,22 @@
           <t>69964204</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4444,7 +4470,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AG Net Lease III LLC</t>
+          <t xml:space="preserve">  AG Net Lease III LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4452,22 +4478,22 @@
           <t>52138946</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4479,7 +4505,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Avenger Parent Inc</t>
+          <t xml:space="preserve">  Avenger Parent Inc</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4487,7 +4513,7 @@
           <t>72342664</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4502,7 +4528,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4514,7 +4540,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Altus Power Inc</t>
+          <t xml:space="preserve">    Altus Power Inc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4522,22 +4548,22 @@
           <t>69264541</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4549,7 +4575,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>APA Generation LLC</t>
+          <t xml:space="preserve">      APA Generation LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4557,22 +4583,22 @@
           <t>70756166</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4584,7 +4610,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Altus Power America Inc</t>
+          <t xml:space="preserve">      Altus Power America Inc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4592,22 +4618,22 @@
           <t>47391568</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4619,7 +4645,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>APA Finance III Borrower LLC</t>
+          <t xml:space="preserve">      APA Finance III Borrower LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4627,22 +4653,22 @@
           <t>71061164</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4654,7 +4680,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>APA Generation Holdings LLC</t>
+          <t xml:space="preserve">      APA Generation Holdings LLC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4662,22 +4688,22 @@
           <t>71431462</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4689,7 +4715,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>APA Finance II LLC</t>
+          <t xml:space="preserve">      APA Finance II LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4697,22 +4723,22 @@
           <t>70641283</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4724,7 +4750,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Aareon AG</t>
+          <t xml:space="preserve">  Aareon AG</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4732,22 +4758,22 @@
           <t>11106369</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4759,7 +4785,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Blue Cloud Pediatric Surgery Centers LLC</t>
+          <t xml:space="preserve">  Blue Cloud Pediatric Surgery Centers LLC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4767,22 +4793,22 @@
           <t>70001350</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4794,7 +4820,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Greencross Pty Ltd</t>
+          <t xml:space="preserve">  Greencross Pty Ltd</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4802,22 +4828,22 @@
           <t>11962245</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4829,7 +4855,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TPG Operating Group II LP</t>
+          <t xml:space="preserve">  TPG Operating Group II LP</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4837,22 +4863,22 @@
           <t>69327531</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4864,7 +4890,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TPG Opco Admin LP</t>
+          <t xml:space="preserve">    TPG Opco Admin LP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4872,22 +4898,22 @@
           <t>70557019</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4899,7 +4925,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TPG Holdings II Sub LP</t>
+          <t xml:space="preserve">    TPG Holdings II Sub LP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4907,22 +4933,22 @@
           <t>45801872</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4934,7 +4960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TPG Operating Group III LP</t>
+          <t xml:space="preserve">    TPG Operating Group III LP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4942,22 +4968,22 @@
           <t>70557021</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4969,7 +4995,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Angelo Gordon &amp; Co LP</t>
+          <t xml:space="preserve">  Angelo Gordon &amp; Co LP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4977,7 +5003,7 @@
           <t>805082</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4992,7 +5018,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5004,7 +5030,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AG Realty Value Fund X LP</t>
+          <t xml:space="preserve">    AG Realty Value Fund X LP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5012,22 +5038,22 @@
           <t>62713452</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5039,7 +5065,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AG Realty Fund VIII LP</t>
+          <t xml:space="preserve">    AG Realty Fund VIII LP</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5047,22 +5073,22 @@
           <t>29555269</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5074,7 +5100,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TPG AG Credit Solutions Fund III LP</t>
+          <t xml:space="preserve">    TPG AG Credit Solutions Fund III LP</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5082,22 +5108,22 @@
           <t>71691216</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5109,7 +5135,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Oak Street Lending LLC</t>
+          <t xml:space="preserve">    Oak Street Lending LLC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5117,22 +5143,22 @@
           <t>34748201</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5144,7 +5170,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AG Realty Value Fund XI LP</t>
+          <t xml:space="preserve">    AG Realty Value Fund XI LP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5152,22 +5178,22 @@
           <t>70025881</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5179,7 +5205,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AG Acquisition J BVI Ltd</t>
+          <t xml:space="preserve">    AG Acquisition J BVI Ltd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5187,22 +5213,22 @@
           <t>32740428</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5214,7 +5240,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Angelo Gordon &amp; Co LP/Private Equity</t>
+          <t xml:space="preserve">    Angelo Gordon &amp; Co LP/Private Equity</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5222,7 +5248,7 @@
           <t>23048064</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5237,7 +5263,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5249,7 +5275,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AG Realty Value Fund X A LP</t>
+          <t xml:space="preserve">      AG Realty Value Fund X A LP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5257,22 +5283,22 @@
           <t>60635956</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5284,7 +5310,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TPG Twin Brook Capital Income Fund</t>
+          <t xml:space="preserve">      TPG Twin Brook Capital Income Fund</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5292,22 +5318,22 @@
           <t>70784743</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5319,7 +5345,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AGTB Private BDC</t>
+          <t xml:space="preserve">        AGTB Private BDC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5327,7 +5353,7 @@
           <t>70451419</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5342,7 +5368,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5354,7 +5380,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Twin Brook Capital Funding XXXIII ASPV LLC</t>
+          <t xml:space="preserve">          Twin Brook Capital Funding XXXIII ASPV LLC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5362,22 +5388,22 @@
           <t>71421530</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5389,7 +5415,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BSC Asi Buyer LLC</t>
+          <t xml:space="preserve">        BSC Asi Buyer LLC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5397,22 +5423,22 @@
           <t>64176350</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5424,7 +5450,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>P20 Global Holdings Inc</t>
+          <t xml:space="preserve">  P20 Global Holdings Inc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5432,22 +5458,22 @@
           <t>65198477</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5459,7 +5485,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>P20 Parent Inc</t>
+          <t xml:space="preserve">    P20 Parent Inc</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5467,22 +5493,22 @@
           <t>70446768</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5494,7 +5520,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Global Governments &amp; Critical Infrastructure Business/Forcepoint LLC</t>
+          <t xml:space="preserve">  Global Governments &amp; Critical Infrastructure Business/Forcepoint LLC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5502,22 +5528,22 @@
           <t>71183935</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5529,7 +5555,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TPG Partners X LP</t>
+          <t xml:space="preserve">  TPG Partners X LP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5537,22 +5563,22 @@
           <t>72471605</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5564,7 +5590,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SureScripts LLC</t>
+          <t xml:space="preserve">  SureScripts LLC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5572,22 +5598,22 @@
           <t>11890750</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5599,7 +5625,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Classic Collision Inc</t>
+          <t xml:space="preserve">  Classic Collision Inc</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5607,22 +5633,22 @@
           <t>66873054</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5634,7 +5660,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Novotech Pty Ltd</t>
+          <t xml:space="preserve">  Novotech Pty Ltd</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5642,22 +5668,22 @@
           <t>17733154</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5669,7 +5695,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ECHO Realty LP</t>
+          <t xml:space="preserve">  ECHO Realty LP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5677,22 +5703,22 @@
           <t>27218240</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5704,7 +5730,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Smith &amp; Howard Advisory LLC</t>
+          <t xml:space="preserve">  Smith &amp; Howard Advisory LLC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5712,22 +5738,22 @@
           <t>71669831</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5739,7 +5765,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Convey Health Solutions Inc</t>
+          <t xml:space="preserve">  Convey Health Solutions Inc</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5747,22 +5773,22 @@
           <t>8122662</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5774,7 +5800,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Grihum Housing Finance Ltd</t>
+          <t xml:space="preserve">  Grihum Housing Finance Ltd</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5782,22 +5808,22 @@
           <t>14725896</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
